--- a/005_品質マネジメント/テスト項目書_シナリオテスト.xlsx
+++ b/005_品質マネジメント/テスト項目書_シナリオテスト.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11210"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanakahda/Desktop/project-management-toolbox/005_品質マネジメント/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1523026-4FB8-C44B-9113-D47E27577812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF580B85-D1EB-F244-A1EB-8D945953E987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17080" xr2:uid="{3802EA87-C52D-F748-9D44-255A88B2D9B6}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>Project：</t>
     <phoneticPr fontId="3"/>
@@ -267,6 +267,21 @@
       <t xml:space="preserve">ガメンメイ </t>
     </rPh>
     <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>項目数</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">コウモクスウ </t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>OK</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>NG</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -1466,7 +1481,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="7.7109375" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="12" style="4" customWidth="1"/>
@@ -1727,7 +1742,7 @@
     <col min="16133" max="16384" width="7.7109375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" ht="18" customHeight="1" thickBot="1">
+    <row r="1" spans="1:7" s="1" customFormat="1" ht="18" customHeight="1" thickBot="1">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1741,12 +1756,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="13.5" customHeight="1" thickBot="1">
+    <row r="2" spans="1:7" ht="13.5" customHeight="1" thickBot="1">
       <c r="A2" s="2"/>
       <c r="B2" s="3"/>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:4" ht="19.5" customHeight="1">
+    <row r="3" spans="1:7" ht="19.5" customHeight="1">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
@@ -1759,16 +1774,37 @@
       <c r="D3" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="34.5" customHeight="1">
+      <c r="E3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="34.5" customHeight="1">
       <c r="A4" s="53">
         <v>1</v>
       </c>
       <c r="B4" s="54"/>
       <c r="C4" s="54"/>
       <c r="D4" s="55"/>
-    </row>
-    <row r="5" spans="1:4" ht="34.5" customHeight="1">
+      <c r="E4" s="4">
+        <f>'1'!G1</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
+        <f>'1'!G2</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="4">
+        <f>'1'!G3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="34.5" customHeight="1">
       <c r="A5" s="53">
         <v>2</v>
       </c>
@@ -1776,7 +1812,7 @@
       <c r="C5" s="54"/>
       <c r="D5" s="56"/>
     </row>
-    <row r="6" spans="1:4" ht="34.5" customHeight="1" thickBot="1">
+    <row r="6" spans="1:7" ht="34.5" customHeight="1" thickBot="1">
       <c r="A6" s="57">
         <v>3</v>
       </c>
